--- a/리베티코리아_3개월_운영자금_요청.xlsx
+++ b/리베티코리아_3개월_운영자금_요청.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,10 +70,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
@@ -81,6 +77,16 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF8A9A99"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -153,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,21 +173,21 @@
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -190,29 +196,34 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -580,14 +591,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -611,19 +622,19 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>요청 총액</t>
         </is>
       </c>
       <c r="C5" s="5">
-        <f>상세내역!D29</f>
-        <v>51194588</v>
+        <f>상세내역!E29</f>
+        <v>43193588</v>
       </c>
       <c r="D5" s="6">
         <f>C5*0.11</f>
-        <v>5631404.68</v>
+        <v>4751294.68</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -638,16 +649,16 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>상세내역!D27</f>
-        <v>37649588</v>
+        <f>상세내역!E27</f>
+        <v>29648588</v>
       </c>
       <c r="D6" s="10">
         <f>C6*0.11</f>
-        <v>4141454.68</v>
+        <v>3261344.68</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>①+②+③+⑤  회수되지 않고 소진되는 비용</t>
+          <t>①+②+③+⑤  회수되지 않고 없어지는 돈</t>
         </is>
       </c>
     </row>
@@ -658,7 +669,7 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>상세내역!D28</f>
+        <f>상세내역!E28</f>
         <v>13545000</v>
       </c>
       <c r="D7" s="10">
@@ -667,7 +678,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>④  스마트스토어 정산으로 회수 → 다음 달 재사용</t>
+          <t>④  정산으로 회수 → 다음 달 재사용</t>
         </is>
       </c>
     </row>
@@ -713,10 +724,10 @@
         </is>
       </c>
       <c r="C11" s="15">
-        <f>상세내역!D10</f>
+        <f>상세내역!E10</f>
         <v>17385000</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="10">
         <f>C11*0.11</f>
         <v>1912350</v>
       </c>
@@ -737,17 +748,17 @@
           <t>3개월 마케팅·운영비</t>
         </is>
       </c>
-      <c r="C12" s="15">
-        <f>상세내역!D18</f>
-        <v>15960000</v>
-      </c>
-      <c r="D12" s="16">
+      <c r="C12" s="16">
+        <f>상세내역!E18</f>
+        <v>8340000</v>
+      </c>
+      <c r="D12" s="10">
         <f>C12*0.11</f>
-        <v>1755600</v>
+        <v>917400</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>광고비·택배비·교통비 등</t>
+          <t>★ 절감 반영 (기존 15,960,000원)</t>
         </is>
       </c>
     </row>
@@ -763,10 +774,10 @@
         </is>
       </c>
       <c r="C13" s="15">
-        <f>상세내역!D23</f>
+        <f>상세내역!E23</f>
         <v>2511750</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="10">
         <f>C13*0.11</f>
         <v>276292.5</v>
       </c>
@@ -788,12 +799,12 @@
         </is>
       </c>
       <c r="C14" s="15">
-        <f>상세내역!D25</f>
-        <v>1792838</v>
-      </c>
-      <c r="D14" s="16">
+        <f>상세내역!E25</f>
+        <v>1411838</v>
+      </c>
+      <c r="D14" s="10">
         <f>C14*0.11</f>
-        <v>197212.18</v>
+        <v>155302.18</v>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
@@ -809,12 +820,12 @@
         </is>
       </c>
       <c r="C15" s="18">
-        <f>상세내역!D27</f>
-        <v>37649588</v>
+        <f>상세내역!E27</f>
+        <v>29648588</v>
       </c>
       <c r="D15" s="19">
         <f>C15*0.11</f>
-        <v>4141454.68</v>
+        <v>3261344.68</v>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
@@ -834,10 +845,10 @@
         </is>
       </c>
       <c r="C16" s="20">
-        <f>상세내역!D28</f>
+        <f>상세내역!E28</f>
         <v>13545000</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="10">
         <f>C16*0.11</f>
         <v>1489950</v>
       </c>
@@ -859,60 +870,217 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>상세내역!D29</f>
-        <v>51194588</v>
+        <f>상세내역!E29</f>
+        <v>43193588</v>
       </c>
       <c r="D17" s="24">
         <f>C17*0.11</f>
-        <v>5631404.68</v>
+        <v>4751294.68</v>
       </c>
       <c r="E17" s="25" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>절감 내역 (마케팅·운영비)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>기존 (월)</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>절감 후 (월)</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>차이</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>메타 광고비</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="n">
+        <v>3960000</v>
+      </c>
+      <c r="D21" s="27" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E21" s="28">
+        <f>D21-C21</f>
+        <v>-1960000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr"/>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>네이버·쿠팡 마케팅</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D22" s="27" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E22" s="28">
+        <f>D22-C22</f>
+        <v>-200000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>택배비</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E23" s="26">
+        <f>D23-C23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>교통비·출장</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>650000</v>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E24" s="28">
+        <f>D24-C24</f>
+        <v>-350000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr"/>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>기타 운영비</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E25" s="28">
+        <f>D25-C25</f>
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr"/>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>3개월 합계</t>
+        </is>
+      </c>
+      <c r="C26" s="18">
+        <f>SUM(C21:C25)*3</f>
+        <v>15960000</v>
+      </c>
+      <c r="D26" s="18">
+        <f>SUM(D21:D25)*3</f>
+        <v>8340000</v>
+      </c>
+      <c r="E26" s="29">
+        <f>D26-C26</f>
+        <v>-7620000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>注記</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>◆ 요청 총액 51,194,588원 중 13,545,000원은 가배송 회전자금입니다. 주문 후 스마트스토어 정산으로 회수되어 다음 달 가배송에 재사용되므로, 실제로 소진되는 금액은 37,649,588원입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>◆ 세금계산서 발행 수수료(2,031,750원)는 발생 가능성이 있는 조건부 비용입니다. 발생하지 않을 경우 요청 총액은 49,061,250원으로 줄어듭니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>◆ 촬영·콘텐츠 제작비와 EMS 비용은 이번 산정에서 제외했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>◆ 요청 총액이 51,194,588원 → 43,193,588원으로 8,001,000원(-15.6%) 줄었습니다. (엔 환산 ¥5,631,405 → ¥4,751,295)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>◆ 요청 총액 43,193,588원 중 13,545,000원은 가배송 회전자금입니다. 정산으로 회수되어 다시 쓰므로, 실제로 없어지는 돈은 29,648,588원입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>◆ 메타 광고비를 실적(3,960,000원/월)의 절반인 2,000,000원/월로 잡았습니다. 10월은 재고가 22개뿐이라 대규모 집행이 불가능하고, 11월 입고 후 단계적으로 늘리는 전제입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>◆ 출장비(항공 980,000 + 숙박 135,500)는 이번 3개월 산정에서 제외했습니다. 촬영·콘텐츠 제작비와 EMS도 제외 상태입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>◆ 세금계산서 수수료(2,031,750원)가 발생하지 않으면 총액은 41,060,250원으로 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>◆ 상품 매입 대금과 800개 통관 비용은 이 요청에 포함되지 않았습니다 (별도 건).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A21:E21"/>
+  <mergeCells count="12">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -925,16 +1093,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,7 +1116,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「실적」은 2025.12~2026.08 실제 지출에서 산출한 값, 「예상치」는 근거를 명시한 가정치입니다.</t>
+          <t>「실적」은 2025.12~2026.08 실제 지출에서 산출, 「예상치」는 근거를 명시한 가정치입니다.</t>
         </is>
       </c>
     </row>
@@ -960,32 +1129,37 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>월액</t>
+          <t>기존(월)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
+          <t>절감 후(월)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
           <t>3개월</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>엔 환산</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>산정 근거</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>①</t>
         </is>
@@ -1000,6 +1174,7 @@
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -1008,23 +1183,26 @@
           <t xml:space="preserve">  인건비</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="26" t="n">
         <v>5000000</v>
       </c>
-      <c r="D6" s="27">
-        <f>C6*3</f>
+      <c r="D6" s="26" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*3</f>
         <v>15000000</v>
       </c>
-      <c r="E6" s="16">
-        <f>D6*0.11</f>
+      <c r="F6" s="10">
+        <f>E6*0.11</f>
         <v>1650000</v>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>지정 금액</t>
         </is>
@@ -1037,23 +1215,26 @@
           <t xml:space="preserve">  세무비</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="26" t="n">
         <v>80000</v>
       </c>
-      <c r="D7" s="27">
-        <f>C7*3</f>
+      <c r="D7" s="26" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E7" s="26">
+        <f>D7*3</f>
         <v>240000</v>
       </c>
-      <c r="E7" s="16">
-        <f>D7*0.11</f>
+      <c r="F7" s="10">
+        <f>E7*0.11</f>
         <v>26400</v>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>지정 금액</t>
         </is>
@@ -1066,23 +1247,26 @@
           <t xml:space="preserve">  사무실 월세</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="26" t="n">
         <v>550000</v>
       </c>
-      <c r="D8" s="27">
-        <f>C8*3</f>
+      <c r="D8" s="26" t="n">
+        <v>550000</v>
+      </c>
+      <c r="E8" s="26">
+        <f>D8*3</f>
         <v>1650000</v>
       </c>
-      <c r="E8" s="16">
-        <f>D8*0.11</f>
+      <c r="F8" s="10">
+        <f>E8*0.11</f>
         <v>181500</v>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>지정 금액</t>
         </is>
@@ -1095,23 +1279,26 @@
           <t xml:space="preserve">  관리비</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="26" t="n">
         <v>165000</v>
       </c>
-      <c r="D9" s="27">
-        <f>C9*3</f>
+      <c r="D9" s="26" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E9" s="26">
+        <f>D9*3</f>
         <v>495000</v>
       </c>
-      <c r="E9" s="16">
-        <f>D9*0.11</f>
+      <c r="F9" s="10">
+        <f>E9*0.11</f>
         <v>54450</v>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>지정 금액</t>
         </is>
@@ -1130,17 +1317,21 @@
       </c>
       <c r="D10" s="18">
         <f>SUM(D6:D9)</f>
+        <v>5795000</v>
+      </c>
+      <c r="E10" s="18">
+        <f>SUM(E6:E9)</f>
         <v>17385000</v>
       </c>
-      <c r="E10" s="19">
-        <f>D10*0.11</f>
+      <c r="F10" s="19">
+        <f>E10*0.11</f>
         <v>1912350</v>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>②</t>
         </is>
@@ -1155,149 +1346,165 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="26" customHeight="1">
+      <c r="H12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="11" t="inlineStr"/>
       <c r="B13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  메타 광고비</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="33" t="n">
         <v>3960000</v>
       </c>
-      <c r="D13" s="27">
-        <f>C13*3</f>
-        <v>11880000</v>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*0.11</f>
-        <v>1306800</v>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>실적</t>
-        </is>
-      </c>
-      <c r="G13" s="30" t="inlineStr">
-        <is>
-          <t>7/18–8/19 집행 실적액 (부가세 포함)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
+      <c r="D13" s="34" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E13" s="26">
+        <f>D13*3</f>
+        <v>6000000</v>
+      </c>
+      <c r="F13" s="10">
+        <f>E13*0.11</f>
+        <v>660000</v>
+      </c>
+      <c r="G13" s="35" t="inlineStr">
+        <is>
+          <t>절감</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="inlineStr">
+        <is>
+          <t>실적 3,960,000은 7/18–8/19 집중 집행분. 10월은 재고 22개뿐이라 대규모 집행 불가, 11월 입고 후 단계적 확대 전제로 절반 수준</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="11" t="inlineStr"/>
       <c r="B14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  네이버·쿠팡 마케팅</t>
         </is>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="33" t="n">
         <v>500000</v>
       </c>
-      <c r="D14" s="27">
-        <f>C14*3</f>
-        <v>1500000</v>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*0.11</f>
-        <v>165000</v>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>예상치</t>
-        </is>
-      </c>
-      <c r="G14" s="30" t="inlineStr">
-        <is>
-          <t>실적 광고 130,000 + SNS 21,700 = 151,700 기준, 재개분 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
+      <c r="D14" s="34" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E14" s="26">
+        <f>D14*3</f>
+        <v>900000</v>
+      </c>
+      <c r="F14" s="10">
+        <f>E14*0.11</f>
+        <v>99000</v>
+      </c>
+      <c r="G14" s="35" t="inlineStr">
+        <is>
+          <t>절감</t>
+        </is>
+      </c>
+      <c r="H14" s="36" t="inlineStr">
+        <is>
+          <t>실적 기준 151,700원/월. 재개분을 감안해 실적의 약 2배로 축소</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="11" t="inlineStr"/>
       <c r="B15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  택배비</t>
         </is>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="33" t="n">
         <v>60000</v>
       </c>
-      <c r="D15" s="27">
-        <f>C15*3</f>
+      <c r="D15" s="37" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="26">
+        <f>D15*3</f>
         <v>180000</v>
       </c>
-      <c r="E15" s="16">
-        <f>D15*0.11</f>
+      <c r="F15" s="10">
+        <f>E15*0.11</f>
         <v>19800</v>
       </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>실적</t>
-        </is>
-      </c>
-      <c r="G15" s="30" t="inlineStr">
-        <is>
-          <t>실적 420,300 ÷ 7회 = 60,043 반올림 (EMS 제외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
+      <c r="G15" s="31" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="inlineStr">
+        <is>
+          <t>실적 420,300÷7회=60,043. 이미 최소 수준이라 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="11" t="inlineStr"/>
       <c r="B16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  교통비·출장</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="33" t="n">
         <v>650000</v>
       </c>
-      <c r="D16" s="27">
-        <f>C16*3</f>
-        <v>1950000</v>
-      </c>
-      <c r="E16" s="16">
-        <f>D16*0.11</f>
-        <v>214500</v>
-      </c>
-      <c r="F16" s="28" t="inlineStr">
-        <is>
-          <t>실적</t>
-        </is>
-      </c>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t>교통 256,667 + 주차 25,550 + 항공·숙박 3개월1회 371,833</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
+      <c r="D16" s="34" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E16" s="26">
+        <f>D16*3</f>
+        <v>900000</v>
+      </c>
+      <c r="F16" s="10">
+        <f>E16*0.11</f>
+        <v>99000</v>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>절감</t>
+        </is>
+      </c>
+      <c r="H16" s="36" t="inlineStr">
+        <is>
+          <t>출장(항공 980,000+숙박 135,500)을 제외. 일상 교통 256,667 + 주차 25,550 = 282,217 반올림</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="11" t="inlineStr"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  기타 운영비</t>
         </is>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="33" t="n">
         <v>150000</v>
       </c>
-      <c r="D17" s="27">
-        <f>C17*3</f>
-        <v>450000</v>
-      </c>
-      <c r="E17" s="16">
-        <f>D17*0.11</f>
-        <v>49500</v>
-      </c>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>실적</t>
-        </is>
-      </c>
-      <c r="G17" s="30" t="inlineStr">
-        <is>
-          <t>휴대폰 55,500 + 기타 49,000 + 소프트웨어 9,900</t>
+      <c r="D17" s="34" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E17" s="26">
+        <f>D17*3</f>
+        <v>360000</v>
+      </c>
+      <c r="F17" s="10">
+        <f>E17*0.11</f>
+        <v>39600</v>
+      </c>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>절감</t>
+        </is>
+      </c>
+      <c r="H17" s="36" t="inlineStr">
+        <is>
+          <t>실적 휴대폰 55,500+기타 49,000+소프트웨어 9,900=114,400 반올림</t>
         </is>
       </c>
     </row>
@@ -1314,17 +1521,21 @@
       </c>
       <c r="D18" s="18">
         <f>SUM(D13:D17)</f>
-        <v>15960000</v>
-      </c>
-      <c r="E18" s="19">
-        <f>D18*0.11</f>
-        <v>1755600</v>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
+        <v>2780000</v>
+      </c>
+      <c r="E18" s="18">
+        <f>SUM(E13:E17)</f>
+        <v>8340000</v>
+      </c>
+      <c r="F18" s="19">
+        <f>E18*0.11</f>
+        <v>917400</v>
+      </c>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>③</t>
         </is>
@@ -1339,6 +1550,7 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="11" t="inlineStr"/>
@@ -1348,19 +1560,20 @@
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr"/>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="11" t="inlineStr"/>
+      <c r="E21" s="26" t="n">
         <v>480000</v>
       </c>
-      <c r="E21" s="16">
-        <f>D21*0.11</f>
+      <c r="F21" s="10">
+        <f>E21*0.11</f>
         <v>52800</v>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="G21" s="30" t="inlineStr">
+      <c r="H21" s="36" t="inlineStr">
         <is>
           <t>6개월 960,000원의 3개월분 (건당 3,000원 × 165건)</t>
         </is>
@@ -1374,19 +1587,20 @@
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr"/>
-      <c r="D22" s="31" t="n">
+      <c r="D22" s="11" t="inlineStr"/>
+      <c r="E22" s="38" t="n">
         <v>2031750</v>
       </c>
-      <c r="E22" s="16">
-        <f>D22*0.11</f>
+      <c r="F22" s="10">
+        <f>E22*0.11</f>
         <v>223492.5</v>
       </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="G22" s="39" t="inlineStr">
         <is>
           <t>조건부</t>
         </is>
       </c>
-      <c r="G22" s="30" t="inlineStr">
+      <c r="H22" s="36" t="inlineStr">
         <is>
           <t>가배송 주문액 13,545,000 × 5% × 3개월</t>
         </is>
@@ -1399,17 +1613,18 @@
           <t>③ 소계</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr"/>
-      <c r="D23" s="18">
-        <f>SUM(D21:D22)</f>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="18">
+        <f>SUM(E21:E22)</f>
         <v>2511750</v>
       </c>
-      <c r="E23" s="19">
-        <f>D23*0.11</f>
+      <c r="F23" s="19">
+        <f>E23*0.11</f>
         <v>276292.5</v>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
@@ -1417,26 +1632,27 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>예비비</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr"/>
-      <c r="D25" s="35">
-        <f>ROUND((D10+D18+D23)*0.05,0)</f>
-        <v>1792838</v>
-      </c>
-      <c r="E25" s="16">
-        <f>D25*0.11</f>
-        <v>197212.18</v>
-      </c>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="41">
+        <f>ROUND((E10+E18+E23)*0.05,0)</f>
+        <v>1411838</v>
+      </c>
+      <c r="F25" s="10">
+        <f>E25*0.11</f>
+        <v>155302.18</v>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
         <is>
           <t>예상치</t>
         </is>
       </c>
-      <c r="G25" s="30" t="inlineStr">
+      <c r="H25" s="36" t="inlineStr">
         <is>
           <t>(①+②+③) × 5%. 환율 변동·긴급 대응용. 일반적인 10%보다 보수적으로 설정</t>
         </is>
@@ -1449,17 +1665,18 @@
           <t>실제 소진 소계 (①+②+③+⑤)</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="36">
-        <f>D10+D18+D23+D25</f>
-        <v>37649588</v>
-      </c>
-      <c r="E27" s="19">
-        <f>D27*0.11</f>
-        <v>4141454.68</v>
-      </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="42">
+        <f>E10+E18+E23+E25</f>
+        <v>29648588</v>
+      </c>
+      <c r="F27" s="19">
+        <f>E27*0.11</f>
+        <v>3261344.68</v>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
@@ -1467,25 +1684,26 @@
           <t>④</t>
         </is>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>가배송 회전 운영자금 (1개월분)</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr"/>
-      <c r="D28" s="37" t="n">
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n">
         <v>13545000</v>
       </c>
-      <c r="E28" s="38">
-        <f>D28*0.11</f>
+      <c r="F28" s="43">
+        <f>E28*0.11</f>
         <v>1489950</v>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="G28" s="31" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="G28" s="30" t="inlineStr">
+      <c r="H28" s="36" t="inlineStr">
         <is>
           <t>S 30개×219,000 + M 25개×279,000. 정산으로 회수되어 다음 달 재사용</t>
         </is>
@@ -1502,22 +1720,23 @@
           <t>요청 총액</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr"/>
-      <c r="D29" s="23">
-        <f>D27+D28</f>
-        <v>51194588</v>
-      </c>
-      <c r="E29" s="24">
-        <f>D29*0.11</f>
-        <v>5631404.68</v>
-      </c>
-      <c r="F29" s="25" t="inlineStr"/>
-      <c r="G29" s="25" t="inlineStr"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="23">
+        <f>E27+E28</f>
+        <v>43193588</v>
+      </c>
+      <c r="F29" s="24">
+        <f>E29*0.11</f>
+        <v>4751294.68</v>
+      </c>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1533,11 +1752,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1550,7 +1769,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1개월차에 가배송 회전자금이 한 번에 들어가므로 첫 달이 큽니다. 2개월차부터는 동일합니다.</t>
+          <t>1개월차에 가배송 회전자금이 한 번에 들어가므로 첫 달만 큽니다. 2개월차부터는 동일합니다.</t>
         </is>
       </c>
     </row>
@@ -1592,16 +1811,16 @@
           <t>① 고정비</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="26" t="n">
         <v>5795000</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="26" t="n">
         <v>5795000</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="26" t="n">
         <v>5795000</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="26">
         <f>SUM(B5:D5)</f>
         <v>17385000</v>
       </c>
@@ -1617,22 +1836,22 @@
           <t>② 마케팅·운영비</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>5320000</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>5320000</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>5320000</v>
-      </c>
-      <c r="E6" s="27">
+      <c r="B6" s="26" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="E6" s="26">
         <f>SUM(B6:D6)</f>
-        <v>15960000</v>
+        <v>8340000</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>매월 동일</t>
+          <t>절감 반영</t>
         </is>
       </c>
     </row>
@@ -1642,16 +1861,16 @@
           <t>③ 가배송 배송비·수수료</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="26" t="n">
         <v>837250</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="26" t="n">
         <v>837250</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="26" t="n">
         <v>837250</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="26">
         <f>SUM(B7:D7)</f>
         <v>2511750</v>
       </c>
@@ -1667,18 +1886,18 @@
           <t>⑤ 예비비</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>597612.6666666666</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>597612.6666666666</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>597612.6666666666</v>
-      </c>
-      <c r="E8" s="27">
+      <c r="B8" s="26" t="n">
+        <v>470612.6666666667</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>470612.6666666667</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>470612.6666666667</v>
+      </c>
+      <c r="E8" s="26">
         <f>SUM(B8:D8)</f>
-        <v>1792838</v>
+        <v>1411838</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
@@ -1692,12 +1911,12 @@
           <t>④ 가배송 회전 운영자금</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="44" t="n">
         <v>13545000</v>
       </c>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27">
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26">
         <f>SUM(B9:D9)</f>
         <v>13545000</v>
       </c>
@@ -1713,21 +1932,21 @@
           <t>월 소요액</t>
         </is>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="45">
         <f>SUM(A5:A9)</f>
-        <v>26094862.666666664</v>
-      </c>
-      <c r="C10" s="40">
+        <v>23427862.666666664</v>
+      </c>
+      <c r="C10" s="45">
         <f>SUM(B5:B9)</f>
-        <v>12549862.666666666</v>
-      </c>
-      <c r="D10" s="40">
+        <v>9882862.666666666</v>
+      </c>
+      <c r="D10" s="45">
         <f>SUM(C5:C9)</f>
-        <v>12549862.666666666</v>
-      </c>
-      <c r="E10" s="40">
+        <v>9882862.666666666</v>
+      </c>
+      <c r="E10" s="45">
         <f>SUM(B10:D10)</f>
-        <v>51194588</v>
+        <v>43193588</v>
       </c>
       <c r="F10" s="25" t="inlineStr"/>
     </row>
@@ -1737,21 +1956,21 @@
           <t>엔 환산</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="10">
         <f>A10*0.11</f>
-        <v>2870434.893333333</v>
-      </c>
-      <c r="C11" s="16">
+        <v>2577064.893333333</v>
+      </c>
+      <c r="C11" s="10">
         <f>B10*0.11</f>
-        <v>1380484.8933333333</v>
-      </c>
-      <c r="D11" s="16">
+        <v>1087114.8933333333</v>
+      </c>
+      <c r="D11" s="10">
         <f>C10*0.11</f>
-        <v>1380484.8933333333</v>
-      </c>
-      <c r="E11" s="16">
+        <v>1087114.8933333333</v>
+      </c>
+      <c r="E11" s="10">
         <f>E10*0.11</f>
-        <v>5631404.68</v>
+        <v>4751294.68</v>
       </c>
       <c r="F11" s="11" t="inlineStr"/>
     </row>
@@ -1765,7 +1984,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>◆ 1개월차 26,094,863원 (¥2,870,435) / 2~3개월차 각 12,549,863원 (¥1,380,485)</t>
+          <t>◆ 1개월차 23,427,863원 (¥2,577,065) / 2~3개월차 각 9,882,863원 (¥1,087,115)</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1998,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>◆ 참고: 현재 재고 22개 기준으로는 월 55건 가배송이 어렵습니다. 800개 입고(11월 중순) 이후 본격 진행이 가능하므로, 필요 시 회전자금 투입 시점을 2개월차로 조정할 수 있습니다.</t>
+          <t>◆ 현재 재고 22개 기준으로는 월 55건 가배송이 어렵습니다. 800개 입고(11월 중순) 이후 본격 진행이 가능하므로, 필요 시 회전자금 투입을 2개월차로 조정할 수 있습니다.</t>
         </is>
       </c>
     </row>
